--- a/Data_clean/MCAS/Estados_US/Edos_USA_2023/DISTRICT_OF_COLUMBIA_2023.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2023/DISTRICT_OF_COLUMBIA_2023.xlsx
@@ -351,40 +351,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES</t>
+          <t>Aguascalientes</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES</t>
+          <t>Aguascalientes</t>
         </is>
       </c>
       <c r="C2">
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PABELLÓN DE ARTEAGA</t>
+          <t>Pabellón De Arteaga</t>
         </is>
       </c>
       <c r="C3">
@@ -408,9 +413,14 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C4">
@@ -423,12 +433,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BAJA CALIFORNIA</t>
+          <t>Baja California</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TIJUANA</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="C5">
@@ -439,9 +449,14 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C6">
@@ -454,12 +469,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAMPECHE</t>
+          <t>Campeche</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CARMEN</t>
+          <t>Carmen</t>
         </is>
       </c>
       <c r="C7">
@@ -470,9 +485,14 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C8">
@@ -485,12 +505,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHIAPAS</t>
+          <t>Chiapas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMATENANGO DE LA FRONTERA</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C9">
@@ -501,9 +521,14 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ESCUINTLA</t>
+          <t>Escuintla</t>
         </is>
       </c>
       <c r="C10">
@@ -514,9 +539,14 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PALENQUE</t>
+          <t>Palenque</t>
         </is>
       </c>
       <c r="C11">
@@ -527,9 +557,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TAPACHULA</t>
+          <t>Tapachula</t>
         </is>
       </c>
       <c r="C12">
@@ -540,9 +575,14 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TONALÁ</t>
+          <t>Tonalá</t>
         </is>
       </c>
       <c r="C13">
@@ -553,9 +593,14 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VILLA CORZO</t>
+          <t>Villa Corzo</t>
         </is>
       </c>
       <c r="C14">
@@ -566,9 +611,14 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C15">
@@ -581,12 +631,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CHIHUAHUA</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JUÁREZ</t>
+          <t>Juárez</t>
         </is>
       </c>
       <c r="C16">
@@ -597,9 +647,14 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C17">
@@ -612,12 +667,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CIUDAD DE MÉXICO</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BENITO JUÁREZ</t>
+          <t>Benito Juárez</t>
         </is>
       </c>
       <c r="C18">
@@ -628,9 +683,14 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CUAUHTÉMOC</t>
+          <t>Cuauhtémoc</t>
         </is>
       </c>
       <c r="C19">
@@ -641,9 +701,14 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GUSTAVO A. MADERO</t>
+          <t>Gustavo A. Madero</t>
         </is>
       </c>
       <c r="C20">
@@ -654,9 +719,14 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IZTAPALAPA</t>
+          <t>Iztapalapa</t>
         </is>
       </c>
       <c r="C21">
@@ -667,9 +737,14 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LA MAGDALENA CONTRERAS</t>
+          <t>La Magdalena Contreras</t>
         </is>
       </c>
       <c r="C22">
@@ -680,9 +755,14 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MIGUEL HIDALGO</t>
+          <t>Miguel Hidalgo</t>
         </is>
       </c>
       <c r="C23">
@@ -693,9 +773,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NO SE REGISTRÓ EL MUNICIPIO/CONDADO/ALCALDÍA DE NACIMIENTO</t>
+          <t>No Se Registró El Municipio/Condado/Alcaldía De Nacimiento</t>
         </is>
       </c>
       <c r="C24">
@@ -706,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VENUSTIANO CARRANZA</t>
+          <t>Venustiano Carranza</t>
         </is>
       </c>
       <c r="C25">
@@ -719,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ÁLVARO OBREGÓN</t>
+          <t>Álvaro Obregón</t>
         </is>
       </c>
       <c r="C26">
@@ -732,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C27">
@@ -747,12 +847,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ESTADO DE MÉXICO</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IXTLAHUACA</t>
+          <t>Ixtlahuaca</t>
         </is>
       </c>
       <c r="C28">
@@ -763,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MORELOS</t>
+          <t>Morelos</t>
         </is>
       </c>
       <c r="C29">
@@ -776,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NEZAHUALCÓYOTL</t>
+          <t>Nezahualcóyotl</t>
         </is>
       </c>
       <c r="C30">
@@ -789,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SAN FELIPE DEL PROGRESO</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C31">
@@ -802,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SAN JOSÉ DEL RINCÓN</t>
+          <t>San José Del Rincón</t>
         </is>
       </c>
       <c r="C32">
@@ -815,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TEMASCALCINGO</t>
+          <t>Temascalcingo</t>
         </is>
       </c>
       <c r="C33">
@@ -828,9 +953,14 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TEOLOYUCAN</t>
+          <t>Teoloyucan</t>
         </is>
       </c>
       <c r="C34">
@@ -841,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TOLUCA</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="C35">
@@ -854,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TULTITLÁN</t>
+          <t>Tultitlán</t>
         </is>
       </c>
       <c r="C36">
@@ -867,9 +1007,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C37">
@@ -882,12 +1027,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ACAPULCO DE JUÁREZ</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C38">
@@ -898,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ACATEPEC</t>
+          <t>Acatepec</t>
         </is>
       </c>
       <c r="C39">
@@ -911,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AHUACUOTZINGO</t>
+          <t>Ahuacuotzingo</t>
         </is>
       </c>
       <c r="C40">
@@ -924,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ALCOZAUCA DE GUERRERO</t>
+          <t>Alcozauca De Guerrero</t>
         </is>
       </c>
       <c r="C41">
@@ -937,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ATENANGO DEL RÍO</t>
+          <t>Atenango Del Río</t>
         </is>
       </c>
       <c r="C42">
@@ -950,9 +1115,14 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ATLIXTAC</t>
+          <t>Atlixtac</t>
         </is>
       </c>
       <c r="C43">
@@ -963,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CHILAPA DE ÁLVAREZ</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C44">
@@ -976,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CHILPANCINGO DE LOS BRAVO</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C45">
@@ -989,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>COAHUAYUTLA DE JOSÉ MARÍA IZAZAGA</t>
+          <t>Coahuayutla De José María Izazaga</t>
         </is>
       </c>
       <c r="C46">
@@ -1002,9 +1187,14 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>COPANATOYAC</t>
+          <t>Copanatoyac</t>
         </is>
       </c>
       <c r="C47">
@@ -1015,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CUALÁC</t>
+          <t>Cualác</t>
         </is>
       </c>
       <c r="C48">
@@ -1028,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EDUARDO NERI</t>
+          <t>Eduardo Neri</t>
         </is>
       </c>
       <c r="C49">
@@ -1041,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>OLINALÁ</t>
+          <t>Olinalá</t>
         </is>
       </c>
       <c r="C50">
@@ -1054,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OMETEPEC</t>
+          <t>Ometepec</t>
         </is>
       </c>
       <c r="C51">
@@ -1067,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SAN MIGUEL TOTOLAPAN</t>
+          <t>San Miguel Totolapan</t>
         </is>
       </c>
       <c r="C52">
@@ -1080,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TLACOAPA</t>
+          <t>Tlacoapa</t>
         </is>
       </c>
       <c r="C53">
@@ -1093,9 +1313,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TLAPA DE COMONFORT</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C54">
@@ -1106,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZITLALA</t>
+          <t>Zitlala</t>
         </is>
       </c>
       <c r="C55">
@@ -1119,9 +1349,14 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C56">
@@ -1134,12 +1369,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>Hidalgo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>APAN</t>
+          <t>Apan</t>
         </is>
       </c>
       <c r="C57">
@@ -1150,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C58">
@@ -1165,12 +1405,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MICHOACÁN DE OCAMPO</t>
+          <t>Michoacán De Ocampo</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>APATZINGÁN</t>
+          <t>Apatzingán</t>
         </is>
       </c>
       <c r="C59">
@@ -1181,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C60">
@@ -1196,12 +1441,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MORELOS</t>
+          <t>Morelos</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CUAUTLA</t>
+          <t>Cuautla</t>
         </is>
       </c>
       <c r="C61">
@@ -1212,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TLAQUILTENANGO</t>
+          <t>Tlaquiltenango</t>
         </is>
       </c>
       <c r="C62">
@@ -1225,9 +1475,14 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>YECAPIXTLA</t>
+          <t>Yecapixtla</t>
         </is>
       </c>
       <c r="C63">
@@ -1238,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ZACATEPEC</t>
+          <t>Zacatepec</t>
         </is>
       </c>
       <c r="C64">
@@ -1251,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C65">
@@ -1266,12 +1531,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>OAXACA</t>
+          <t>Oaxaca</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CHAHUITES</t>
+          <t>Chahuites</t>
         </is>
       </c>
       <c r="C66">
@@ -1282,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CHALCATONGO DE HIDALGO</t>
+          <t>Chalcatongo De Hidalgo</t>
         </is>
       </c>
       <c r="C67">
@@ -1295,9 +1565,14 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HEROICA CIUDAD DE JUCHITÁN DE ZARAGOZA</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C68">
@@ -1308,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OAXACA DE JUÁREZ</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C69">
@@ -1321,9 +1601,14 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DEL MAR</t>
+          <t>San Francisco Del Mar</t>
         </is>
       </c>
       <c r="C70">
@@ -1334,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO TELIXTLAHUACA</t>
+          <t>San Francisco Telixtlahuaca</t>
         </is>
       </c>
       <c r="C71">
@@ -1347,9 +1637,14 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA JAYACATLÁN</t>
+          <t>San Juan Bautista Jayacatlán</t>
         </is>
       </c>
       <c r="C72">
@@ -1360,9 +1655,14 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA TUXTEPEC</t>
+          <t>San Juan Bautista Tuxtepec</t>
         </is>
       </c>
       <c r="C73">
@@ -1373,9 +1673,14 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA VALLE NACIONAL</t>
+          <t>San Juan Bautista Valle Nacional</t>
         </is>
       </c>
       <c r="C74">
@@ -1386,9 +1691,14 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SAN PABLO HUITZO</t>
+          <t>San Pablo Huitzo</t>
         </is>
       </c>
       <c r="C75">
@@ -1399,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAN PEDRO POCHUTLA</t>
+          <t>San Pedro Pochutla</t>
         </is>
       </c>
       <c r="C76">
@@ -1412,9 +1727,14 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SANTA CATARINA LACHATAO</t>
+          <t>Santa Catarina Lachatao</t>
         </is>
       </c>
       <c r="C77">
@@ -1425,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SANTIAGO JAMILTEPEC</t>
+          <t>Santiago Jamiltepec</t>
         </is>
       </c>
       <c r="C78">
@@ -1438,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C79">
@@ -1453,12 +1783,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ACATZINGO</t>
+          <t>Acatzingo</t>
         </is>
       </c>
       <c r="C80">
@@ -1469,9 +1799,14 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CHAPULCO</t>
+          <t>Chapulco</t>
         </is>
       </c>
       <c r="C81">
@@ -1482,9 +1817,14 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CHICHIQUILA</t>
+          <t>Chichiquila</t>
         </is>
       </c>
       <c r="C82">
@@ -1495,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EPATLÁN</t>
+          <t>Epatlán</t>
         </is>
       </c>
       <c r="C83">
@@ -1508,9 +1853,14 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GENERAL FELIPE ÁNGELES</t>
+          <t>General Felipe Ángeles</t>
         </is>
       </c>
       <c r="C84">
@@ -1521,9 +1871,14 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IXCAMILPA DE GUERRERO</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C85">
@@ -1534,9 +1889,14 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IXCAQUIXTLA</t>
+          <t>Ixcaquixtla</t>
         </is>
       </c>
       <c r="C86">
@@ -1547,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IZÚCAR DE MATAMOROS</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C87">
@@ -1560,9 +1925,14 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LOS REYES DE JUÁREZ</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C88">
@@ -1573,9 +1943,14 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NEALTICAN</t>
+          <t>Nealtican</t>
         </is>
       </c>
       <c r="C89">
@@ -1586,9 +1961,14 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SANTIAGO MIAHUATLÁN</t>
+          <t>Santiago Miahuatlán</t>
         </is>
       </c>
       <c r="C90">
@@ -1599,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TEHUACÁN</t>
+          <t>Tehuacán</t>
         </is>
       </c>
       <c r="C91">
@@ -1612,9 +1997,14 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TEHUITZINGO</t>
+          <t>Tehuitzingo</t>
         </is>
       </c>
       <c r="C92">
@@ -1625,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TEPANCO DE LÓPEZ</t>
+          <t>Tepanco De López</t>
         </is>
       </c>
       <c r="C93">
@@ -1638,9 +2033,14 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TLACOTEPEC DE BENITO JUÁREZ</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C94">
@@ -1651,9 +2051,14 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VICENTE GUERRERO</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C95">
@@ -1664,9 +2069,14 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZACAPOAXTLA</t>
+          <t>Zacapoaxtla</t>
         </is>
       </c>
       <c r="C96">
@@ -1677,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C97">
@@ -1692,12 +2107,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SAN JUAN DEL RÍO</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C98">
@@ -1708,9 +2123,14 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C99">
@@ -1723,12 +2143,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>QUINTANA ROO</t>
+          <t>Quintana Roo</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>OTHÓN P. BLANCO</t>
+          <t>Othón P. Blanco</t>
         </is>
       </c>
       <c r="C100">
@@ -1739,9 +2159,14 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C101">
@@ -1754,12 +2179,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SONORA</t>
+          <t>Sonora</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ALAMOS</t>
+          <t>Alamos</t>
         </is>
       </c>
       <c r="C102">
@@ -1770,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C103">
@@ -1785,12 +2215,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TAMAULIPAS</t>
+          <t>Tamaulipas</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TAMPICO</t>
+          <t>Tampico</t>
         </is>
       </c>
       <c r="C104">
@@ -1801,9 +2231,14 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C105">
@@ -1816,12 +2251,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TLAXCALA</t>
+          <t>Tlaxcala</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>APIZACO</t>
+          <t>Apizaco</t>
         </is>
       </c>
       <c r="C106">
@@ -1832,9 +2267,14 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TEPEYANCO</t>
+          <t>Tepeyanco</t>
         </is>
       </c>
       <c r="C107">
@@ -1845,9 +2285,14 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TETLA DE LA SOLIDARIDAD</t>
+          <t>Tetla De La Solidaridad</t>
         </is>
       </c>
       <c r="C108">
@@ -1858,9 +2303,14 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TLAXCALA</t>
+          <t>Tlaxcala</t>
         </is>
       </c>
       <c r="C109">
@@ -1871,9 +2321,14 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TOCATLÁN</t>
+          <t>Tocatlán</t>
         </is>
       </c>
       <c r="C110">
@@ -1884,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>YAUHQUEMEHCAN</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C111">
@@ -1897,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C112">
@@ -1912,12 +2377,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+          <t>Veracruz De Ignacio De La Llave</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>AMATLÁN DE LOS REYES</t>
+          <t>Amatlán De Los Reyes</t>
         </is>
       </c>
       <c r="C113">
@@ -1928,9 +2393,14 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CÓRDOBA</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="C114">
@@ -1941,9 +2411,14 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MARTÍNEZ DE LA TORRE</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C115">
@@ -1954,9 +2429,14 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SAN ANDRÉS TUXTLA</t>
+          <t>San Andrés Tuxtla</t>
         </is>
       </c>
       <c r="C116">
@@ -1967,9 +2447,14 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TANTOYUCA</t>
+          <t>Tantoyuca</t>
         </is>
       </c>
       <c r="C117">
@@ -1980,9 +2465,14 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TUXPAN</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C118">
@@ -1993,9 +2483,14 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>VERACRUZ</t>
+          <t>Veracruz</t>
         </is>
       </c>
       <c r="C119">
@@ -2006,9 +2501,14 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>XALAPA</t>
+          <t>Xalapa</t>
         </is>
       </c>
       <c r="C120">
@@ -2019,9 +2519,14 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>YANGA</t>
+          <t>Yanga</t>
         </is>
       </c>
       <c r="C121">
@@ -2032,9 +2537,14 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C122">
@@ -2047,7 +2557,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C123">
@@ -2055,41 +2565,6 @@
       </c>
       <c r="D123">
         <v>1</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 789,030</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de Mexicanas y Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Noviembre de 2024</t>
-        </is>
       </c>
     </row>
   </sheetData>
